--- a/Upwork_Templates/13. PTO_Leave_Tracker.xlsx
+++ b/Upwork_Templates/13. PTO_Leave_Tracker.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pvipi\Desktop\VIP_GitHub\Excel_Projects\Upwork_Templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{845CB63F-D567-4917-9FBA-4334A52D1829}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF89ED42-90EE-40E1-B030-E6084FD64B3C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{DD2CA759-2D62-44FC-A426-DE024F2B9B46}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{DD2CA759-2D62-44FC-A426-DE024F2B9B46}"/>
   </bookViews>
   <sheets>
     <sheet name="Employee_Master" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="69">
   <si>
     <t>ID</t>
   </si>
@@ -121,16 +121,151 @@
   </si>
   <si>
     <t>Carry Forward</t>
+  </si>
+  <si>
+    <t>E1000</t>
+  </si>
+  <si>
+    <t>E1001</t>
+  </si>
+  <si>
+    <t>E1002</t>
+  </si>
+  <si>
+    <t>E1003</t>
+  </si>
+  <si>
+    <t>E1004</t>
+  </si>
+  <si>
+    <t>E1005</t>
+  </si>
+  <si>
+    <t>E1006</t>
+  </si>
+  <si>
+    <t>E1007</t>
+  </si>
+  <si>
+    <t>E1008</t>
+  </si>
+  <si>
+    <t>E1009</t>
+  </si>
+  <si>
+    <t>E1010</t>
+  </si>
+  <si>
+    <t>E1011</t>
+  </si>
+  <si>
+    <t>E1012</t>
+  </si>
+  <si>
+    <t>E1013</t>
+  </si>
+  <si>
+    <t>E1014</t>
+  </si>
+  <si>
+    <t>E1015</t>
+  </si>
+  <si>
+    <t>E1016</t>
+  </si>
+  <si>
+    <t>E1017</t>
+  </si>
+  <si>
+    <t>E1018</t>
+  </si>
+  <si>
+    <t>Vipin Pandey</t>
+  </si>
+  <si>
+    <t>Amandeep Singh</t>
+  </si>
+  <si>
+    <t>Honyei Konyak</t>
+  </si>
+  <si>
+    <t>Pavinai Paite</t>
+  </si>
+  <si>
+    <t>Sanjay Pandey</t>
+  </si>
+  <si>
+    <t>Sinam Robert</t>
+  </si>
+  <si>
+    <t>Aagosh Khinda</t>
+  </si>
+  <si>
+    <t>Dimple Saxena</t>
+  </si>
+  <si>
+    <t>Kanishka Chaudhary</t>
+  </si>
+  <si>
+    <t>Chiraag Madan</t>
+  </si>
+  <si>
+    <t>Aryan Mishra</t>
+  </si>
+  <si>
+    <t>Manvi Singh</t>
+  </si>
+  <si>
+    <t>Paneet Kaur</t>
+  </si>
+  <si>
+    <t>Bhawri Gupta</t>
+  </si>
+  <si>
+    <t>Rajdeep Gogoi</t>
+  </si>
+  <si>
+    <t>Khavine Joycy</t>
+  </si>
+  <si>
+    <t>Mathew</t>
+  </si>
+  <si>
+    <t>Utkarsh Dubey</t>
+  </si>
+  <si>
+    <t>Ankit Shukla</t>
+  </si>
+  <si>
+    <t>E1019</t>
+  </si>
+  <si>
+    <t>E1020</t>
+  </si>
+  <si>
+    <t>Shova Chetri</t>
+  </si>
+  <si>
+    <t>Sonali Roy</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <numFmts count="1">
+    <numFmt numFmtId="170" formatCode="0.0"/>
+  </numFmts>
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -156,9 +291,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -495,10 +633,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{199A00A1-57EF-4CCE-A582-FA2BCA12F16E}">
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F22"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="3" width="8.88671875" style="1"/>
+    <col min="1" max="1" width="8.88671875" style="1"/>
+    <col min="2" max="2" width="17.77734375" style="1" customWidth="1"/>
+    <col min="3" max="3" width="8.88671875" style="1"/>
     <col min="4" max="4" width="13.109375" style="1" customWidth="1"/>
     <col min="5" max="5" width="15.6640625" style="1" customWidth="1"/>
     <col min="6" max="6" width="13" style="1" customWidth="1"/>
@@ -525,12 +665,182 @@
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="E2" s="1">
+      <c r="A2" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="D2" s="1">
+        <v>25</v>
+      </c>
+      <c r="E2" s="2">
         <f>D2/12</f>
-        <v>0</v>
+        <v>2.0833333333333335</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A4" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A5" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A6" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A7" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A8" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A9" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A10" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A11" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A12" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A13" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A14" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A15" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A16" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A17" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A18" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A19" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A20" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A21" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A22" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>68</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -540,8 +850,8 @@
   <dimension ref="A1:F2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="5" style="1" customWidth="1"/>
-    <col min="2" max="2" width="8.33203125" style="1" customWidth="1"/>
+    <col min="1" max="1" width="7.109375" style="1" customWidth="1"/>
+    <col min="2" max="2" width="18" style="1" customWidth="1"/>
     <col min="3" max="3" width="11.6640625" style="1" customWidth="1"/>
     <col min="4" max="4" width="10.88671875" style="1" customWidth="1"/>
     <col min="5" max="5" width="10.109375" style="1" customWidth="1"/>
@@ -569,6 +879,9 @@
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
+        <v>27</v>
+      </c>
       <c r="F2" s="1">
         <f>NETWORKDAYS(D2,E2)</f>
         <v>0</v>
@@ -576,62 +889,81 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{B7736085-E700-4EBF-A1C0-00F1DD64CE24}">
+          <x14:formula1>
+            <xm:f>Employee_Master!$A$2:$A$22</xm:f>
+          </x14:formula1>
+          <xm:sqref>A1:A1048576</xm:sqref>
+        </x14:dataValidation>
+      </x14:dataValidations>
+    </ext>
+  </extLst>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BB158FAC-2CD5-4ED2-BC91-EBBA3679A6B6}">
-  <dimension ref="A1:N1"/>
+  <dimension ref="A1:N2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="11" max="11" width="10.44140625" customWidth="1"/>
-    <col min="12" max="12" width="9.88671875" customWidth="1"/>
-    <col min="13" max="13" width="9.33203125" customWidth="1"/>
-    <col min="14" max="14" width="9.5546875" customWidth="1"/>
+    <col min="1" max="10" width="8.88671875" style="1"/>
+    <col min="11" max="11" width="10.44140625" style="1" customWidth="1"/>
+    <col min="12" max="12" width="9.88671875" style="1" customWidth="1"/>
+    <col min="13" max="13" width="9.33203125" style="1" customWidth="1"/>
+    <col min="14" max="14" width="9.5546875" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
+      <c r="A1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="K1" t="s">
+      <c r="K1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="L1" t="s">
+      <c r="L1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="M1" t="s">
+      <c r="M1" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="N1" t="s">
+      <c r="N1" s="1" t="s">
         <v>17</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="C2" s="1">
+        <f>SUMIFS(Leave_log!F:F, Leave_log!A:A, $A2, Leave_log!D:D, "&gt;=01-Jan-2026", Leave_log!D:D, "&lt;=31-Jan-2026")</f>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/Upwork_Templates/13. PTO_Leave_Tracker.xlsx
+++ b/Upwork_Templates/13. PTO_Leave_Tracker.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pvipi\Desktop\VIP_GitHub\Excel_Projects\Upwork_Templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF89ED42-90EE-40E1-B030-E6084FD64B3C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49356B5E-72D7-46C5-9D43-87259725B297}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{DD2CA759-2D62-44FC-A426-DE024F2B9B46}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="71">
   <si>
     <t>ID</t>
   </si>
@@ -247,6 +247,12 @@
   </si>
   <si>
     <t>Sonali Roy</t>
+  </si>
+  <si>
+    <t>E1021</t>
+  </si>
+  <si>
+    <t>Sana Qadir</t>
   </si>
 </sst>
 </file>
@@ -254,7 +260,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="170" formatCode="0.0"/>
+    <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
@@ -296,7 +302,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -633,7 +639,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{199A00A1-57EF-4CCE-A582-FA2BCA12F16E}">
-  <dimension ref="A1:F22"/>
+  <dimension ref="A1:F23"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="8.88671875" style="1"/>
@@ -839,6 +845,14 @@
         <v>68</v>
       </c>
     </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A23" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>70</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -847,7 +861,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{86D16CE7-7E5C-45E5-8D8D-6BA57DFF5892}">
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="7.109375" style="1" customWidth="1"/>
@@ -880,11 +894,33 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
+      </c>
+      <c r="B2" s="1" t="str">
+        <f>_xlfn.XLOOKUP(A2, Employee_Master!A:A, Employee_Master!B:B, "")</f>
+        <v>Honyei Konyak</v>
       </c>
       <c r="F2" s="1">
         <f>NETWORKDAYS(D2,E2)</f>
         <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B3" s="1" t="str">
+        <f>_xlfn.XLOOKUP(A3, Employee_Master!A:A, Employee_Master!B:B, "")</f>
+        <v>Kanishka Chaudhary</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A4" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B4" s="1" t="str">
+        <f>_xlfn.XLOOKUP(A4, Employee_Master!A:A, Employee_Master!B:B, "")</f>
+        <v>Aryan Mishra</v>
       </c>
     </row>
   </sheetData>
